--- a/inst/plantillas/plantilla_inrs.xlsx
+++ b/inst/plantillas/plantilla_inrs.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INRS_datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -559,14 +559,14 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>expoquimR · Plantilla INRS</t>
+          <t>expoquimR · INRS Template</t>
         </is>
       </c>
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Instrucciones: una fila por producto. frases_h / frases_r: separadas por comas. cantidad_unidad: g / ml / kg / l. frecuencia_unidad: minutos / horas / dias / meses / no_se_usa. tipo_sustancia: liquida / solida. metodo_liquido: grafico / presion (solo liquidas). procedimiento: Dispersivo / Abierto / Cerrado/abierto regularmente / Cerrado permanente. proteccion: ver hoja Instrucciones.</t>
+          <t>Instructions: one row per product. h_phrases / r_phrases: comma-separated. quantity_unit: g / ml / kg / l. frequency_unit: minutes / hours / days / months / not_used. substance_type: liquid / solid. liquid_method: graph / pressure (liquids only). procedure: Dispersive / Open / Closed/opened regularly / Permanently closed. protection: see Instructions sheet.</t>
         </is>
       </c>
       <c r="B2" s="3" t="n"/>
@@ -590,22 +590,22 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>producto</t>
+          <t>product</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>frases_h</t>
+          <t>h_phrases</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>frases_r</t>
+          <t>r_phrases</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>proceso</t>
+          <t>process</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -615,69 +615,69 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>cantidad_valor</t>
+          <t>quantity_value</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>cantidad_unidad</t>
+          <t>quantity_unit</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>frecuencia_valor</t>
+          <t>frequency_value</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>frecuencia_unidad</t>
+          <t>frequency_unit</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>tipo_sustancia</t>
+          <t>substance_type</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>metodo_liquido</t>
+          <t>liquid_method</t>
         </is>
       </c>
       <c r="L3" s="5" t="inlineStr">
         <is>
-          <t>temperatura_uso</t>
+          <t>use_temperature</t>
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr">
         <is>
-          <t>punto_ebullicion</t>
+          <t>boiling_point</t>
         </is>
       </c>
       <c r="N3" s="5" t="inlineStr">
         <is>
-          <t>presion_vapor</t>
+          <t>vapour_pressure</t>
         </is>
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
-          <t>descripcion_solida</t>
+          <t>solid_description</t>
         </is>
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>procedimiento</t>
+          <t>procedure</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>proteccion</t>
+          <t>protection</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tolueno</t>
+          <t>Toluene</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -703,17 +703,17 @@
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
-          <t>horas</t>
+          <t>hours</t>
         </is>
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>liquida</t>
+          <t>liquid</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>grafico</t>
+          <t>graph</t>
         </is>
       </c>
       <c r="L4" s="6" t="n">
@@ -726,19 +726,19 @@
       <c r="O4" s="6" t="inlineStr"/>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
         <is>
-          <t>Condiciones moderadas de dispersion</t>
+          <t>Moderate dispersion conditions</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Cemento</t>
+          <t>Cement</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
@@ -749,7 +749,7 @@
       <c r="C5" s="6" t="inlineStr"/>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>cemento</t>
+          <t>cement</t>
         </is>
       </c>
       <c r="E5" s="6" t="n">
@@ -768,12 +768,12 @@
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>horas</t>
+          <t>hours</t>
         </is>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>solida</t>
+          <t>solid</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr"/>
@@ -782,17 +782,17 @@
       <c r="N5" s="6" t="inlineStr"/>
       <c r="O5" s="6" t="inlineStr">
         <is>
-          <t>Polvo fino con poca dispersion visible</t>
+          <t>Fine dust with little visible dispersion</t>
         </is>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>Abierto</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="Q5" s="6" t="inlineStr">
         <is>
-          <t>Sin ventilacion mecanica</t>
+          <t>No mechanical ventilation</t>
         </is>
       </c>
     </row>
@@ -821,55 +821,55 @@
     <row r="1">
       <c r="A1" s="7" t="inlineStr">
         <is>
-          <t>Campo</t>
+          <t>Field</t>
         </is>
       </c>
       <c r="B1" s="7" t="inlineStr">
         <is>
-          <t>Valores aceptados</t>
+          <t>Accepted values</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>procedimiento</t>
+          <t>procedure</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Dispersivo | Abierto | Cerrado/abierto regularmente | Cerrado permanente</t>
+          <t>Dispersive | Open | Closed/opened regularly | Permanently closed</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>proteccion</t>
+          <t>protection</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Espacio confinado sin ventilacion | Sin ventilacion mecanica | Condiciones moderadas de dispersion | Captacion localizada o cabinas ventiladas | Captacion envolvente</t>
+          <t>Confined space without ventilation | No mechanical ventilation | Moderate dispersion conditions | Local exhaust or ventilated enclosures | Enclosing hood / full enclosure</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>descripcion_solida</t>
+          <t>solid_description</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Polvo que genera mucha dispersion visible en el aire | Polvo fino con poca dispersion visible | Solido compacto sin polvo visible</t>
+          <t>Dust that generates a lot of visible dispersion in the air | Fine dust with little visible dispersion | Compact solid with no visible dust</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>cantidad_unidad</t>
+          <t>quantity_unit</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -881,36 +881,36 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>frecuencia_unidad</t>
+          <t>frequency_unit</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>minutos | horas | dias | meses | no_se_usa</t>
+          <t>minutes | hours | days | months | not_used</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>tipo_sustancia</t>
+          <t>substance_type</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>liquida | solida</t>
+          <t>liquid | solid</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>metodo_liquido</t>
+          <t>liquid_method</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>grafico | presion (solo si tipo_sustancia=liquida)</t>
+          <t>graph | pressure (only if substance_type=liquid)</t>
         </is>
       </c>
     </row>
